--- a/小挖常见工况竞品量化评分.xlsx
+++ b/小挖常见工况竞品量化评分.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="C2" t="n">
         <v>0.973</v>
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57.6</v>
+        <v>57.5</v>
       </c>
       <c r="C3" t="n">
         <v>0.973</v>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53.9</v>
+        <v>54.6</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8</v>
+        <v>0.804</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>52.2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.651</v>
+        <v>0.659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="C7" t="n">
         <v>0.89</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46.7</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
         <v>0.974</v>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.848</v>
+        <v>0.85</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43.2</v>
+        <v>43.7</v>
       </c>
       <c r="C10" t="n">
         <v>0.843</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.799</v>
+        <v>0.801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -746,11 +746,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XCMG XE35U</t>
+          <t>沃尔沃 EC37</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>22.3</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -777,11 +777,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>卡特 303.5CR</t>
+          <t>现代 HX35AZ</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>45.6</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -839,18 +839,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>山猫 E35</t>
+          <t>卡特 303.5CR</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.3</v>
+        <v>45.5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -870,18 +870,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>久保田 U35</t>
+          <t>山猫 E35</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>43.6</v>
+        <v>38.4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0.58</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -901,11 +901,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>久保田 KX033</t>
+          <t>斗山 DX35Z-7</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>39.6</v>
+        <v>46.8</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -932,11 +932,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>沃尔沃 EC37</t>
+          <t>XCMG XE35U</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.3</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>现代 HX35AZ</t>
+          <t>久保田 KX033</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>39.7</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -994,18 +994,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>斗山 DX35Z-7</t>
+          <t>三一 SY35U</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>46.8</v>
+        <v>40.9</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1025,18 +1025,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>三一 SY35U</t>
+          <t>久保田 U35</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40.9</v>
+        <v>43.6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XCMG XE35U</t>
+          <t>沃尔沃 EC37</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>55.8</v>
+        <v>43.1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1087,14 +1087,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>卡特 303.5CR</t>
+          <t>现代 HX35AZ</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31.8</v>
+        <v>45.2</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1149,18 +1149,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>山猫 E35</t>
+          <t>卡特 303.5CR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>48.9</v>
+        <v>31.8</v>
       </c>
       <c r="D15" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1180,18 +1180,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>久保田 U35</t>
+          <t>山猫 E35</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>32.6</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1211,14 +1211,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>久保田 KX033</t>
+          <t>斗山 DX35Z-7</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>51.7</v>
+        <v>85.5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1242,14 +1242,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>沃尔沃 EC37</t>
+          <t>XCMG XE35U</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>43.1</v>
+        <v>55.8</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1273,14 +1273,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>现代 HX35AZ</t>
+          <t>久保田 KX033</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>45.2</v>
+        <v>51.8</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1304,18 +1304,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>斗山 DX35Z-7</t>
+          <t>三一 SY35U</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>85.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1335,18 +1335,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>三一 SY35U</t>
+          <t>久保田 U35</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57.5</v>
+        <v>32.7</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1366,11 +1366,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XCMG XE35U</t>
+          <t>沃尔沃 EC37</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>54.9</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1397,11 +1397,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>卡特 303.5CR</t>
+          <t>现代 HX35AZ</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>55</v>
+        <v>69.5</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>42.8</v>
+        <v>46.1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1459,18 +1459,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>山猫 E35</t>
+          <t>卡特 303.5CR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>63.9</v>
+        <v>55.6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1490,18 +1490,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>久保田 U35</t>
+          <t>山猫 E35</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>65.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9</v>
+        <v>0.658</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1521,18 +1521,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>久保田 KX033</t>
+          <t>斗山 DX35Z-7</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>69</v>
+        <v>33.7</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1552,11 +1552,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>沃尔沃 EC37</t>
+          <t>XCMG XE35U</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>83.59999999999999</v>
+        <v>56.5</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -1583,14 +1583,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>现代 HX35AZ</t>
+          <t>久保田 KX033</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>70.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1614,11 +1614,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>斗山 DX35Z-7</t>
+          <t>三一 SY35U</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>34.1</v>
+        <v>35.6</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
@@ -1645,14 +1645,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>三一 SY35U</t>
+          <t>久保田 U35</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>32.9</v>
+        <v>64.8</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1676,11 +1676,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>XCMG XE35U</t>
+          <t>沃尔沃 EC37</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>51.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -1707,11 +1707,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>卡特 303.5CR</t>
+          <t>现代 HX35AZ</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>51.3</v>
+        <v>81.3</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="D34" t="n">
         <v>0.48</v>
@@ -1769,18 +1769,18 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>山猫 E35</t>
+          <t>卡特 303.5CR</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>56.1</v>
+        <v>51.3</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1800,14 +1800,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>久保田 U35</t>
+          <t>山猫 E35</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>42.3</v>
+        <v>56.2</v>
       </c>
       <c r="D36" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1831,14 +1831,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>久保田 KX033</t>
+          <t>斗山 DX35Z-7</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>42.1</v>
+        <v>21.1</v>
       </c>
       <c r="D37" t="n">
-        <v>0.48</v>
+        <v>0.38</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1862,11 +1862,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>沃尔沃 EC37</t>
+          <t>XCMG XE35U</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>68.40000000000001</v>
+        <v>51.4</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
@@ -1893,18 +1893,18 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>现代 HX35AZ</t>
+          <t>久保田 KX033</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>81.3</v>
+        <v>42.1</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1924,14 +1924,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>斗山 DX35Z-7</t>
+          <t>三一 SY35U</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>21.1</v>
+        <v>55.3</v>
       </c>
       <c r="D40" t="n">
-        <v>0.38</v>
+        <v>0.72</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1955,14 +1955,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>三一 SY35U</t>
+          <t>久保田 U35</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>55.3</v>
+        <v>42.3</v>
       </c>
       <c r="D41" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1986,18 +1986,18 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>XCMG XE35U</t>
+          <t>沃尔沃 EC37</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>52.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>0.855</v>
+        <v>0.909</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2017,14 +2017,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>卡特 303.5CR</t>
+          <t>现代 HX35AZ</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0.909</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="D44" t="n">
         <v>0.6909999999999999</v>
@@ -2079,18 +2079,18 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>山猫 E35</t>
+          <t>卡特 303.5CR</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="D45" t="n">
-        <v>0.509</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2110,14 +2110,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>久保田 U35</t>
+          <t>山猫 E35</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>22</v>
+        <v>39.1</v>
       </c>
       <c r="D46" t="n">
-        <v>0.455</v>
+        <v>0.509</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2141,18 +2141,18 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>久保田 KX033</t>
+          <t>斗山 DX35Z-7</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>18.3</v>
+        <v>47.4</v>
       </c>
       <c r="D47" t="n">
-        <v>0.727</v>
+        <v>1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2172,18 +2172,18 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>沃尔沃 EC37</t>
+          <t>XCMG XE35U</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>64.90000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="D48" t="n">
-        <v>0.909</v>
+        <v>0.855</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2203,18 +2203,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>现代 HX35AZ</t>
+          <t>久保田 KX033</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>59</v>
+        <v>18.4</v>
       </c>
       <c r="D49" t="n">
-        <v>0.909</v>
+        <v>0.727</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2234,18 +2234,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>斗山 DX35Z-7</t>
+          <t>三一 SY35U</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>47.4</v>
+        <v>33.1</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0.855</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2265,18 +2265,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>三一 SY35U</t>
+          <t>久保田 U35</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>33.2</v>
+        <v>22</v>
       </c>
       <c r="D51" t="n">
-        <v>0.855</v>
+        <v>0.455</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2296,11 +2296,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>XCMG XE35U</t>
+          <t>沃尔沃 EC37</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>29.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
@@ -2327,11 +2327,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>卡特 303.5CR</t>
+          <t>现代 HX35AZ</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>58.1</v>
+        <v>49.5</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
@@ -2389,11 +2389,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>山猫 E35</t>
+          <t>卡特 303.5CR</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>65.2</v>
+        <v>58.1</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
@@ -2420,11 +2420,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>久保田 U35</t>
+          <t>山猫 E35</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>46.2</v>
+        <v>65.2</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -2451,11 +2451,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>久保田 KX033</t>
+          <t>斗山 DX35Z-7</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>59.6</v>
+        <v>56.3</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
@@ -2482,11 +2482,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>沃尔沃 EC37</t>
+          <t>XCMG XE35U</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>66.09999999999999</v>
+        <v>29.2</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
@@ -2513,11 +2513,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>现代 HX35AZ</t>
+          <t>久保田 KX033</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>49.5</v>
+        <v>59.6</v>
       </c>
       <c r="D59" t="n">
         <v>1</v>
@@ -2544,11 +2544,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>斗山 DX35Z-7</t>
+          <t>三一 SY35U</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>56.3</v>
+        <v>40.8</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
@@ -2575,11 +2575,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>三一 SY35U</t>
+          <t>久保田 U35</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>40.8</v>
+        <v>46.3</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
@@ -2609,7 +2609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M501"/>
+  <dimension ref="A1:M531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11560,10 +11560,10 @@
         <v>16.5</v>
       </c>
       <c r="J152" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K152" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -11619,10 +11619,10 @@
         <v>64.8</v>
       </c>
       <c r="J153" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K153" t="n">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -11737,10 +11737,10 @@
         <v>58.2</v>
       </c>
       <c r="J155" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K155" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -11796,10 +11796,10 @@
         <v>89</v>
       </c>
       <c r="J156" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K156" t="n">
-        <v>17.8</v>
+        <v>16</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -11855,10 +11855,10 @@
         <v>100</v>
       </c>
       <c r="J157" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K157" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -11914,10 +11914,10 @@
         <v>92.3</v>
       </c>
       <c r="J158" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K158" t="n">
-        <v>18.5</v>
+        <v>16.6</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -11973,10 +11973,10 @@
         <v>56</v>
       </c>
       <c r="J159" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K159" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -12032,10 +12032,10 @@
         <v>51.6</v>
       </c>
       <c r="J160" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K160" t="n">
-        <v>10.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -12091,10 +12091,10 @@
         <v>14.3</v>
       </c>
       <c r="J161" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K161" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -12150,10 +12150,10 @@
         <v>57.4</v>
       </c>
       <c r="J162" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K162" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -12209,10 +12209,10 @@
         <v>31.5</v>
       </c>
       <c r="J163" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K163" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -12268,10 +12268,10 @@
         <v>33.3</v>
       </c>
       <c r="J164" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K164" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -12327,10 +12327,10 @@
         <v>66.7</v>
       </c>
       <c r="J165" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K165" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -12386,10 +12386,10 @@
         <v>48.1</v>
       </c>
       <c r="J166" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K166" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
@@ -12504,10 +12504,10 @@
         <v>100</v>
       </c>
       <c r="J168" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K168" t="n">
-        <v>12</v>
+        <v>10.8</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -12563,10 +12563,10 @@
         <v>50</v>
       </c>
       <c r="J169" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K169" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -12622,10 +12622,10 @@
         <v>66.7</v>
       </c>
       <c r="J170" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K170" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -12681,10 +12681,10 @@
         <v>20.4</v>
       </c>
       <c r="J171" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K171" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -12740,10 +12740,10 @@
         <v>84.5</v>
       </c>
       <c r="J172" t="n">
-        <v>0.16</v>
+        <v>0.144</v>
       </c>
       <c r="K172" t="n">
-        <v>13.5</v>
+        <v>12.2</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -12799,10 +12799,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>0.16</v>
+        <v>0.144</v>
       </c>
       <c r="K173" t="n">
-        <v>13.7</v>
+        <v>12.4</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -12858,10 +12858,10 @@
         <v>85.40000000000001</v>
       </c>
       <c r="J174" t="n">
-        <v>0.16</v>
+        <v>0.144</v>
       </c>
       <c r="K174" t="n">
-        <v>13.7</v>
+        <v>12.3</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>0.16</v>
+        <v>0.144</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -12967,10 +12967,10 @@
         <v>86.09999999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>0.16</v>
+        <v>0.144</v>
       </c>
       <c r="K176" t="n">
-        <v>13.8</v>
+        <v>12.4</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -13026,10 +13026,10 @@
         <v>84.90000000000001</v>
       </c>
       <c r="J177" t="n">
-        <v>0.16</v>
+        <v>0.144</v>
       </c>
       <c r="K177" t="n">
-        <v>13.6</v>
+        <v>12.2</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -13085,10 +13085,10 @@
         <v>100</v>
       </c>
       <c r="J178" t="n">
-        <v>0.16</v>
+        <v>0.144</v>
       </c>
       <c r="K178" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -13144,10 +13144,10 @@
         <v>83</v>
       </c>
       <c r="J179" t="n">
-        <v>0.16</v>
+        <v>0.144</v>
       </c>
       <c r="K179" t="n">
-        <v>13.3</v>
+        <v>12</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>0.16</v>
+        <v>0.144</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>69</v>
       </c>
       <c r="J181" t="n">
-        <v>0.16</v>
+        <v>0.144</v>
       </c>
       <c r="K181" t="n">
-        <v>11</v>
+        <v>9.9</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -13321,10 +13321,10 @@
         <v>100</v>
       </c>
       <c r="J182" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K182" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
@@ -13433,7 +13433,7 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -13639,10 +13639,10 @@
         <v>60</v>
       </c>
       <c r="J188" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K188" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -13698,10 +13698,10 @@
         <v>60</v>
       </c>
       <c r="J189" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K189" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K190" t="n">
         <v>0</v>
@@ -13816,7 +13816,7 @@
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
@@ -13875,10 +13875,10 @@
         <v>63.6</v>
       </c>
       <c r="J192" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K192" t="n">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -13934,10 +13934,10 @@
         <v>63.6</v>
       </c>
       <c r="J193" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K193" t="n">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -13993,10 +13993,10 @@
         <v>63.6</v>
       </c>
       <c r="J194" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K194" t="n">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -14102,10 +14102,10 @@
         <v>54.5</v>
       </c>
       <c r="J196" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K196" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -14161,10 +14161,10 @@
         <v>54.5</v>
       </c>
       <c r="J197" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K197" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -14220,10 +14220,10 @@
         <v>63.6</v>
       </c>
       <c r="J198" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K198" t="n">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -14279,10 +14279,10 @@
         <v>100</v>
       </c>
       <c r="J199" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K199" t="n">
-        <v>12</v>
+        <v>10.8</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
@@ -14397,10 +14397,10 @@
         <v>63.6</v>
       </c>
       <c r="J201" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="K201" t="n">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -14456,10 +14456,10 @@
         <v>100</v>
       </c>
       <c r="J202" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K202" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -14515,10 +14515,10 @@
         <v>52.2</v>
       </c>
       <c r="J203" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K203" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -14574,10 +14574,10 @@
         <v>39.1</v>
       </c>
       <c r="J204" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K204" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -14633,10 +14633,10 @@
         <v>49.6</v>
       </c>
       <c r="J205" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K205" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -14751,10 +14751,10 @@
         <v>69.59999999999999</v>
       </c>
       <c r="J207" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K207" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -14810,10 +14810,10 @@
         <v>42.6</v>
       </c>
       <c r="J208" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K208" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -14869,10 +14869,10 @@
         <v>19.6</v>
       </c>
       <c r="J209" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K209" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>91.3</v>
       </c>
       <c r="J210" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K210" t="n">
-        <v>9.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -14987,10 +14987,10 @@
         <v>39.1</v>
       </c>
       <c r="J211" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K211" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>0</v>
       </c>
       <c r="J212" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
@@ -15105,10 +15105,10 @@
         <v>66.7</v>
       </c>
       <c r="J213" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K213" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -15214,10 +15214,10 @@
         <v>100</v>
       </c>
       <c r="J215" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K215" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -15273,10 +15273,10 @@
         <v>100</v>
       </c>
       <c r="J216" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K216" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -15332,10 +15332,10 @@
         <v>100</v>
       </c>
       <c r="J217" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K217" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -15391,10 +15391,10 @@
         <v>100</v>
       </c>
       <c r="J218" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K218" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -15450,10 +15450,10 @@
         <v>100</v>
       </c>
       <c r="J219" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K219" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -15509,10 +15509,10 @@
         <v>66.7</v>
       </c>
       <c r="J220" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K220" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>0</v>
       </c>
       <c r="J221" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>35.7</v>
       </c>
       <c r="J222" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K222" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -15686,10 +15686,10 @@
         <v>50</v>
       </c>
       <c r="J223" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K223" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -15745,10 +15745,10 @@
         <v>50</v>
       </c>
       <c r="J224" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K224" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -15804,10 +15804,10 @@
         <v>50</v>
       </c>
       <c r="J225" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K225" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -15863,10 +15863,10 @@
         <v>50</v>
       </c>
       <c r="J226" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K226" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -15922,10 +15922,10 @@
         <v>50</v>
       </c>
       <c r="J227" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K227" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -15981,10 +15981,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="J228" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K228" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -16040,10 +16040,10 @@
         <v>100</v>
       </c>
       <c r="J229" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K229" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -16158,10 +16158,10 @@
         <v>50</v>
       </c>
       <c r="J231" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K231" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -31884,6 +31884,1836 @@
       <c r="M501" t="inlineStr">
         <is>
           <t>租赁管理和维保追踪。</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>沃尔沃 EC37</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I502" t="n">
+        <v>100</v>
+      </c>
+      <c r="J502" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K502" t="n">
+        <v>4</v>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>现代 HX35AZ</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I503" t="n">
+        <v>0</v>
+      </c>
+      <c r="J503" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K503" t="n">
+        <v>0</v>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>迪尔 35P</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I504" t="n">
+        <v>100</v>
+      </c>
+      <c r="J504" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K504" t="n">
+        <v>4</v>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>卡特 303.5CR</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I505" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K505" t="n">
+        <v>0</v>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>山猫 E35</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I506" t="n">
+        <v>100</v>
+      </c>
+      <c r="J506" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K506" t="n">
+        <v>4</v>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>斗山 DX35Z-7</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I507" t="n">
+        <v>0</v>
+      </c>
+      <c r="J507" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K507" t="n">
+        <v>0</v>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>XCMG XE35U</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I508" t="n">
+        <v>100</v>
+      </c>
+      <c r="J508" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K508" t="n">
+        <v>4</v>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>久保田 KX033</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I509" t="n">
+        <v>0</v>
+      </c>
+      <c r="J509" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K509" t="n">
+        <v>0</v>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>三一 SY35U</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I510" t="n">
+        <v>0</v>
+      </c>
+      <c r="J510" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K510" t="n">
+        <v>0</v>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>久保田 U35</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I511" t="n">
+        <v>0</v>
+      </c>
+      <c r="J511" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K511" t="n">
+        <v>0</v>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>沃尔沃 EC37</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I512" t="n">
+        <v>100</v>
+      </c>
+      <c r="J512" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K512" t="n">
+        <v>3</v>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>现代 HX35AZ</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I513" t="n">
+        <v>100</v>
+      </c>
+      <c r="J513" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K513" t="n">
+        <v>3</v>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>迪尔 35P</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I514" t="n">
+        <v>100</v>
+      </c>
+      <c r="J514" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K514" t="n">
+        <v>3</v>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>卡特 303.5CR</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I515" t="n">
+        <v>100</v>
+      </c>
+      <c r="J515" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K515" t="n">
+        <v>3</v>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>山猫 E35</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I516" t="n">
+        <v>100</v>
+      </c>
+      <c r="J516" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K516" t="n">
+        <v>3</v>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>斗山 DX35Z-7</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I517" t="n">
+        <v>100</v>
+      </c>
+      <c r="J517" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K517" t="n">
+        <v>3</v>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>XCMG XE35U</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I518" t="n">
+        <v>100</v>
+      </c>
+      <c r="J518" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K518" t="n">
+        <v>3</v>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>久保田 KX033</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I519" t="n">
+        <v>100</v>
+      </c>
+      <c r="J519" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K519" t="n">
+        <v>3</v>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>三一 SY35U</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I520" t="n">
+        <v>100</v>
+      </c>
+      <c r="J520" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K520" t="n">
+        <v>3</v>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>久保田 U35</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I521" t="n">
+        <v>100</v>
+      </c>
+      <c r="J521" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K521" t="n">
+        <v>3</v>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>沃尔沃 EC37</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>选配</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>选配</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I522" t="n">
+        <v>60</v>
+      </c>
+      <c r="J522" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K522" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>现代 HX35AZ</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I523" t="n">
+        <v>100</v>
+      </c>
+      <c r="J523" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K523" t="n">
+        <v>3</v>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>迪尔 35P</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I524" t="n">
+        <v>0</v>
+      </c>
+      <c r="J524" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K524" t="n">
+        <v>0</v>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>卡特 303.5CR</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I525" t="n">
+        <v>100</v>
+      </c>
+      <c r="J525" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K525" t="n">
+        <v>3</v>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>山猫 E35</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I526" t="n">
+        <v>100</v>
+      </c>
+      <c r="J526" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K526" t="n">
+        <v>3</v>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>斗山 DX35Z-7</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I527" t="n">
+        <v>0</v>
+      </c>
+      <c r="J527" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K527" t="n">
+        <v>0</v>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>XCMG XE35U</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I528" t="n">
+        <v>0</v>
+      </c>
+      <c r="J528" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K528" t="n">
+        <v>0</v>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>久保田 KX033</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I529" t="n">
+        <v>100</v>
+      </c>
+      <c r="J529" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K529" t="n">
+        <v>3</v>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>三一 SY35U</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I530" t="n">
+        <v>100</v>
+      </c>
+      <c r="J530" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K530" t="n">
+        <v>3</v>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>久保田 U35</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>标配&gt;选配&gt;无；未披露不参与</t>
+        </is>
+      </c>
+      <c r="I531" t="n">
+        <v>100</v>
+      </c>
+      <c r="J531" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K531" t="n">
+        <v>3</v>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
         </is>
       </c>
     </row>
@@ -31898,7 +33728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -38039,6 +39869,1536 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>沃尔沃 EC37</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>100</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H122" t="n">
+        <v>4</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>现代 HX35AZ</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>迪尔 35P</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>100</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H124" t="n">
+        <v>4</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>卡特 303.5CR</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>山猫 E35</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>100</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H126" t="n">
+        <v>4</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>斗山 DX35Z-7</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>XCMG XE35U</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>100</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>久保田 KX033</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>三一 SY35U</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>经济模式</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>久保田 U35</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>轻载/市政土方循环中用于控制油耗和发动机响应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>沃尔沃 EC37</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>100</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H132" t="n">
+        <v>3</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>现代 HX35AZ</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>100</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H133" t="n">
+        <v>3</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>迪尔 35P</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>100</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H134" t="n">
+        <v>3</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>卡特 303.5CR</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>100</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H135" t="n">
+        <v>3</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>山猫 E35</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>100</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H136" t="n">
+        <v>3</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>斗山 DX35Z-7</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>100</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H137" t="n">
+        <v>3</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>XCMG XE35U</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>100</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H138" t="n">
+        <v>3</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>久保田 KX033</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>100</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H139" t="n">
+        <v>3</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>三一 SY35U</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>100</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H140" t="n">
+        <v>3</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>自动怠速</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>久保田 U35</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>100</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H141" t="n">
+        <v>3</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>等待装车、短暂停顿时降低怠速油耗与噪声。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>沃尔沃 EC37</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>选配</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>选配</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>60</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>现代 HX35AZ</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>100</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H143" t="n">
+        <v>3</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>迪尔 35P</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>卡特 303.5CR</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>100</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H145" t="n">
+        <v>3</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>山猫 E35</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>100</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H146" t="n">
+        <v>3</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>斗山 DX35Z-7</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>XCMG XE35U</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>无配置</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>久保田 KX033</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>100</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H149" t="n">
+        <v>3</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>三一 SY35U</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>100</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H150" t="n">
+        <v>3</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>土方装车 / 短循环效率</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>推土铲浮动</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>久保田 U35</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>100</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H151" t="n">
+        <v>3</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>3-4.xlsx 标选配表</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>回填、整平、清底等土方配套动作效率更高。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38050,7 +41410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -38132,63 +41492,84 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>破碎 / 多属具作业</t>
+          <t>土方装车 / 短循环效率</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XCMG XE35U</t>
+          <t>山猫 E35</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>坡地 / 软土 / 吊装稳定</t>
+          <t>破碎 / 多属具作业</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>现代 HX35AZ</t>
+          <t>XCMG XE35U</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.1</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>坡地 / 软土 / 吊装稳定</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>现代 HX35AZ</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>租赁 / 快速转场 / 多客户通用</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>迪尔 35P</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>29</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>26.8</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -38302,7 +41683,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>铲斗挖掘力、斗杆挖掘力、系统流量、工作压力、回转速度、最大卸载高度、发动机总功率、液压系统</t>
+          <t>铲斗挖掘力、斗杆挖掘力、系统流量、工作压力、回转速度、最大卸载高度、发动机总功率、液压系统、经济模式、自动怠速、推土铲浮动</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -38428,7 +41809,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>标配=100，选配=60，明确无配置=0，空白/未披露不参与评分。</t>
+          <t>标配=100，选配=60，明确无配置=0，空白/未披露不参与评分；土方短循环新增经济模式、自动怠速、推土铲浮动配置贡献。</t>
         </is>
       </c>
     </row>
@@ -38440,7 +41821,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>产品名称已标准化映射：徐工=XCMG，现代/斗山/三一按参数表完整型号对齐。</t>
+          <t>产品名称已标准化映射。</t>
         </is>
       </c>
     </row>

--- a/小挖常见工况竞品量化评分.xlsx
+++ b/小挖常见工况竞品量化评分.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,22 +31,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00263746"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -61,11 +52,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,36 +421,29 @@
   </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>产品</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>综合工况评分</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>平均数据覆盖率</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>综合置信等级</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>原表综合评分</t>
         </is>
@@ -475,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57.8</v>
+        <v>60.7</v>
       </c>
       <c r="C2" t="n">
         <v>0.973</v>
@@ -496,7 +477,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57.5</v>
+        <v>59.4</v>
       </c>
       <c r="C3" t="n">
         <v>0.973</v>
@@ -538,7 +519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.2</v>
+        <v>54.1</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -580,7 +561,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>48.1</v>
+        <v>48.9</v>
       </c>
       <c r="C7" t="n">
         <v>0.89</v>
@@ -601,7 +582,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>48.9</v>
       </c>
       <c r="C8" t="n">
         <v>0.974</v>
@@ -622,7 +603,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46.1</v>
+        <v>46.5</v>
       </c>
       <c r="C9" t="n">
         <v>0.85</v>
@@ -691,48 +672,39 @@
   </sheetPr>
   <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>工况</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>产品</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>工况得分</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>数据覆盖率</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>置信等级</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>工况权重</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>工况说明</t>
         </is>
@@ -750,7 +722,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.3</v>
+        <v>38.5</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -781,7 +753,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>48.5</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -843,7 +815,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.5</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -905,7 +877,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.8</v>
+        <v>51.4</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -936,7 +908,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>38.5</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -967,7 +939,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>39.7</v>
+        <v>42</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -2611,84 +2583,69 @@
   </sheetPr>
   <dimension ref="A1:M531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>工况</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>指标/配置</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>产品</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>原始值</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>数据状态</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>指标得分</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>贡献分</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>相关性说明</t>
         </is>
@@ -4072,6 +4029,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -4087,9 +4045,11 @@
           <t>越低越好</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
         <v>0.24</v>
       </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -4495,13 +4455,13 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.3</v>
+        <v>64.3</v>
       </c>
       <c r="J32" t="n">
         <v>0.18</v>
       </c>
       <c r="K32" t="n">
-        <v>1.1</v>
+        <v>11.6</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -4510,7 +4470,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>贴墙、沟边、障碍物旁作业能力。</t>
+          <t>贴墙、沟边、障碍物旁作业能力；多版本参数按同一版本口径取值，不相加。</t>
         </is>
       </c>
     </row>
@@ -4554,13 +4514,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.3</v>
+        <v>64.3</v>
       </c>
       <c r="J33" t="n">
         <v>0.18</v>
       </c>
       <c r="K33" t="n">
-        <v>1.1</v>
+        <v>11.6</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -4569,7 +4529,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>贴墙、沟边、障碍物旁作业能力。</t>
+          <t>贴墙、沟边、障碍物旁作业能力；多版本参数按同一版本口径取值，不相加。</t>
         </is>
       </c>
     </row>
@@ -4595,11 +4555,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>258</v>
+        <v>130</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>有数据</t>
+          <t>有数据；驾驶室/驾驶棚版本不同不合计，取同一版本较优口径</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4628,7 +4588,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>贴墙、沟边、障碍物旁作业能力。</t>
+          <t>贴墙、沟边、障碍物旁作业能力；多版本参数按同一版本口径取值，不相加。</t>
         </is>
       </c>
     </row>
@@ -4653,6 +4613,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -4668,9 +4629,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
         <v>0.18</v>
       </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -4737,7 +4700,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>贴墙、沟边、障碍物旁作业能力。</t>
+          <t>贴墙、沟边、障碍物旁作业能力；多版本参数按同一版本口径取值，不相加。</t>
         </is>
       </c>
     </row>
@@ -4781,13 +4744,13 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>14.3</v>
       </c>
       <c r="J37" t="n">
         <v>0.18</v>
       </c>
       <c r="K37" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -4796,7 +4759,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>贴墙、沟边、障碍物旁作业能力。</t>
+          <t>贴墙、沟边、障碍物旁作业能力；多版本参数按同一版本口径取值，不相加。</t>
         </is>
       </c>
     </row>
@@ -4840,13 +4803,13 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>9.9</v>
+        <v>100</v>
       </c>
       <c r="J38" t="n">
         <v>0.18</v>
       </c>
       <c r="K38" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4855,7 +4818,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>贴墙、沟边、障碍物旁作业能力。</t>
+          <t>贴墙、沟边、障碍物旁作业能力；多版本参数按同一版本口径取值，不相加。</t>
         </is>
       </c>
     </row>
@@ -4899,13 +4862,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.3</v>
+        <v>64.3</v>
       </c>
       <c r="J39" t="n">
         <v>0.18</v>
       </c>
       <c r="K39" t="n">
-        <v>1.1</v>
+        <v>11.6</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -4914,7 +4877,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>贴墙、沟边、障碍物旁作业能力。</t>
+          <t>贴墙、沟边、障碍物旁作业能力；多版本参数按同一版本口径取值，不相加。</t>
         </is>
       </c>
     </row>
@@ -4958,13 +4921,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>28.6</v>
       </c>
       <c r="J40" t="n">
         <v>0.18</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -4973,7 +4936,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>贴墙、沟边、障碍物旁作业能力。</t>
+          <t>贴墙、沟边、障碍物旁作业能力；多版本参数按同一版本口径取值，不相加。</t>
         </is>
       </c>
     </row>
@@ -4998,6 +4961,7 @@
           <t>三一 SY35U</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -5013,9 +4977,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
         <v>0.18</v>
       </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -7626,6 +7592,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -7641,9 +7608,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
         <v>0.16</v>
       </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -7971,6 +7940,7 @@
           <t>三一 SY35U</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -7986,9 +7956,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="n">
         <v>0.16</v>
       </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -8139,6 +8111,7 @@
           <t>迪尔 35P</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -8154,9 +8127,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
         <v>0.12</v>
       </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -10332,6 +10307,7 @@
           <t>三一 SY35U</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>未披露</t>
@@ -10347,9 +10323,11 @@
           <t>标配&gt;选配&gt;无；未披露不参与</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="n">
         <v>0.08</v>
       </c>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>3-4.xlsx 标选配表</t>
@@ -10748,6 +10726,7 @@
           <t>沃尔沃 EC37</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>未披露</t>
@@ -10763,9 +10742,11 @@
           <t>标配&gt;选配&gt;无；未披露不参与</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="n">
         <v>0.06</v>
       </c>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
           <t>3-4.xlsx 标选配表</t>
@@ -10798,6 +10779,7 @@
           <t>现代 HX35AZ</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>未披露</t>
@@ -10813,9 +10795,11 @@
           <t>标配&gt;选配&gt;无；未披露不参与</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="n">
         <v>0.06</v>
       </c>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
           <t>3-4.xlsx 标选配表</t>
@@ -10848,6 +10832,7 @@
           <t>斗山 DX35Z-7</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>未披露</t>
@@ -10863,9 +10848,11 @@
           <t>标配&gt;选配&gt;无；未披露不参与</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="n">
         <v>0.06</v>
       </c>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
           <t>3-4.xlsx 标选配表</t>
@@ -10898,6 +10885,7 @@
           <t>三一 SY35U</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>未披露</t>
@@ -10913,9 +10901,11 @@
           <t>标配&gt;选配&gt;无；未披露不参与</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="n">
         <v>0.06</v>
       </c>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
           <t>3-4.xlsx 标选配表</t>
@@ -12895,6 +12885,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -12910,9 +12901,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="n">
         <v>0.144</v>
       </c>
+      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -13417,6 +13410,7 @@
           <t>迪尔 35P</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -13432,9 +13426,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="n">
         <v>0.09</v>
       </c>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -13467,6 +13463,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -13482,9 +13479,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr"/>
       <c r="J185" t="n">
         <v>0.09</v>
       </c>
+      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -13517,6 +13516,7 @@
           <t>久保田 U35</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -13532,9 +13532,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="n">
         <v>0.09</v>
       </c>
+      <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -13567,6 +13569,7 @@
           <t>久保田 KX033</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -13582,9 +13585,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="n">
         <v>0.09</v>
       </c>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -14030,6 +14035,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -14045,9 +14051,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr"/>
       <c r="J195" t="n">
         <v>0.108</v>
       </c>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -15142,6 +15150,7 @@
           <t>迪尔 35P</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -15157,9 +15166,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr"/>
       <c r="J214" t="n">
         <v>0.09</v>
       </c>
+      <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -16667,6 +16678,7 @@
           <t>斗山 DX35Z-7</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -16682,9 +16694,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I240" t="inlineStr"/>
       <c r="J240" t="n">
         <v>0.2</v>
       </c>
+      <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -16894,6 +16908,7 @@
           <t>迪尔 35P</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -16909,9 +16924,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I244" t="inlineStr"/>
       <c r="J244" t="n">
         <v>0.14</v>
       </c>
+      <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -17003,6 +17020,7 @@
           <t>久保田 U35</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -17018,9 +17036,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I246" t="inlineStr"/>
       <c r="J246" t="n">
         <v>0.14</v>
       </c>
+      <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -17053,6 +17073,7 @@
           <t>久保田 KX033</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -17068,9 +17089,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I247" t="inlineStr"/>
       <c r="J247" t="n">
         <v>0.14</v>
       </c>
+      <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -17221,6 +17244,7 @@
           <t>斗山 DX35Z-7</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -17236,9 +17260,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr"/>
       <c r="J250" t="n">
         <v>0.14</v>
       </c>
+      <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -17448,6 +17474,7 @@
           <t>迪尔 35P</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -17463,9 +17490,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I254" t="inlineStr"/>
       <c r="J254" t="n">
         <v>0.16</v>
       </c>
+      <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -17498,6 +17527,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -17513,9 +17543,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I255" t="inlineStr"/>
       <c r="J255" t="n">
         <v>0.16</v>
       </c>
+      <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -17548,6 +17580,7 @@
           <t>久保田 U35</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -17563,9 +17596,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I256" t="inlineStr"/>
       <c r="J256" t="n">
         <v>0.16</v>
       </c>
+      <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -17598,6 +17633,7 @@
           <t>久保田 KX033</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -17613,9 +17649,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr"/>
       <c r="J257" t="n">
         <v>0.16</v>
       </c>
+      <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -17766,6 +17804,7 @@
           <t>斗山 DX35Z-7</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -17781,9 +17820,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I260" t="inlineStr"/>
       <c r="J260" t="n">
         <v>0.16</v>
       </c>
+      <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -17816,6 +17857,7 @@
           <t>三一 SY35U</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -17831,9 +17873,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I261" t="inlineStr"/>
       <c r="J261" t="n">
         <v>0.16</v>
       </c>
+      <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -17984,6 +18028,7 @@
           <t>迪尔 35P</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -17999,9 +18044,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I264" t="inlineStr"/>
       <c r="J264" t="n">
         <v>0.12</v>
       </c>
+      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -18034,6 +18081,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -18049,9 +18097,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I265" t="inlineStr"/>
       <c r="J265" t="n">
         <v>0.12</v>
       </c>
+      <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -18084,6 +18134,7 @@
           <t>久保田 U35</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -18099,9 +18150,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I266" t="inlineStr"/>
       <c r="J266" t="n">
         <v>0.12</v>
       </c>
+      <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -18134,6 +18187,7 @@
           <t>久保田 KX033</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -18149,9 +18203,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I267" t="inlineStr"/>
       <c r="J267" t="n">
         <v>0.12</v>
       </c>
+      <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -18302,6 +18358,7 @@
           <t>斗山 DX35Z-7</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -18317,9 +18374,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I270" t="inlineStr"/>
       <c r="J270" t="n">
         <v>0.12</v>
       </c>
+      <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -18352,6 +18411,7 @@
           <t>三一 SY35U</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -18367,9 +18427,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I271" t="inlineStr"/>
       <c r="J271" t="n">
         <v>0.12</v>
       </c>
+      <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -18579,6 +18641,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -18594,9 +18657,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I275" t="inlineStr"/>
       <c r="J275" t="n">
         <v>0.12</v>
       </c>
+      <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -19101,6 +19166,7 @@
           <t>迪尔 35P</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -19116,9 +19182,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I284" t="inlineStr"/>
       <c r="J284" t="n">
         <v>0.1</v>
       </c>
+      <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -19151,6 +19219,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -19166,9 +19235,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I285" t="inlineStr"/>
       <c r="J285" t="n">
         <v>0.1</v>
       </c>
+      <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -19201,6 +19272,7 @@
           <t>久保田 U35</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -19216,9 +19288,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I286" t="inlineStr"/>
       <c r="J286" t="n">
         <v>0.1</v>
       </c>
+      <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -19251,6 +19325,7 @@
           <t>久保田 KX033</t>
         </is>
       </c>
+      <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -19266,9 +19341,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I287" t="inlineStr"/>
       <c r="J287" t="n">
         <v>0.1</v>
       </c>
+      <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -21465,6 +21542,7 @@
           <t>迪尔 35P</t>
         </is>
       </c>
+      <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -21480,9 +21558,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I324" t="inlineStr"/>
       <c r="J324" t="n">
         <v>0.1273</v>
       </c>
+      <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -21515,6 +21595,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -21530,9 +21611,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I325" t="inlineStr"/>
       <c r="J325" t="n">
         <v>0.1273</v>
       </c>
+      <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -22037,6 +22120,7 @@
           <t>迪尔 35P</t>
         </is>
       </c>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -22052,9 +22136,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I334" t="inlineStr"/>
       <c r="J334" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -22087,6 +22173,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -22102,9 +22189,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I335" t="inlineStr"/>
       <c r="J335" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -22137,6 +22226,7 @@
           <t>久保田 U35</t>
         </is>
       </c>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -22152,9 +22242,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I336" t="inlineStr"/>
       <c r="J336" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -22187,6 +22279,7 @@
           <t>久保田 KX033</t>
         </is>
       </c>
+      <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -22202,9 +22295,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I337" t="inlineStr"/>
       <c r="J337" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -22237,6 +22332,7 @@
           <t>沃尔沃 EC37</t>
         </is>
       </c>
+      <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -22252,9 +22348,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I338" t="inlineStr"/>
       <c r="J338" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -22641,6 +22739,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -22656,9 +22755,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I345" t="inlineStr"/>
       <c r="J345" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -23222,6 +23323,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -23237,9 +23339,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I355" t="inlineStr"/>
       <c r="J355" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -23272,6 +23376,7 @@
           <t>久保田 U35</t>
         </is>
       </c>
+      <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -23287,9 +23392,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I356" t="inlineStr"/>
       <c r="J356" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -23322,6 +23429,7 @@
           <t>久保田 KX033</t>
         </is>
       </c>
+      <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -23337,9 +23445,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I357" t="inlineStr"/>
       <c r="J357" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -23608,6 +23718,7 @@
           <t>XCMG XE35U</t>
         </is>
       </c>
+      <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -23623,9 +23734,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I362" t="inlineStr"/>
       <c r="J362" t="n">
         <v>0.1455</v>
       </c>
+      <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -23835,6 +23948,7 @@
           <t>久保田 U35</t>
         </is>
       </c>
+      <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -23850,9 +23964,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I366" t="inlineStr"/>
       <c r="J366" t="n">
         <v>0.1455</v>
       </c>
+      <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -24121,6 +24237,7 @@
           <t>三一 SY35U</t>
         </is>
       </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -24136,9 +24253,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I371" t="inlineStr"/>
       <c r="J371" t="n">
         <v>0.1455</v>
       </c>
+      <c r="K371" t="inlineStr"/>
       <c r="L371" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -24289,6 +24408,7 @@
           <t>迪尔 35P</t>
         </is>
       </c>
+      <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -24304,9 +24424,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I374" t="inlineStr"/>
       <c r="J374" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -24339,6 +24461,7 @@
           <t>山猫 E35</t>
         </is>
       </c>
+      <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -24354,9 +24477,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I375" t="inlineStr"/>
       <c r="J375" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -24389,6 +24514,7 @@
           <t>久保田 U35</t>
         </is>
       </c>
+      <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -24404,9 +24530,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I376" t="inlineStr"/>
       <c r="J376" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -24439,6 +24567,7 @@
           <t>久保田 KX033</t>
         </is>
       </c>
+      <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -24454,9 +24583,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I377" t="inlineStr"/>
       <c r="J377" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -24548,6 +24679,7 @@
           <t>现代 HX35AZ</t>
         </is>
       </c>
+      <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -24563,9 +24695,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I379" t="inlineStr"/>
       <c r="J379" t="n">
         <v>0.09089999999999999</v>
       </c>
+      <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -24952,6 +25086,7 @@
           <t>久保田 U35</t>
         </is>
       </c>
+      <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
           <t>缺失/未披露</t>
@@ -24967,9 +25102,11 @@
           <t>越高越好</t>
         </is>
       </c>
+      <c r="I386" t="inlineStr"/>
       <c r="J386" t="n">
         <v>0.1273</v>
       </c>
+      <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr">
         <is>
           <t>3-4.xlsx 参数表</t>
@@ -33730,72 +33867,59 @@
   </sheetPr>
   <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>工况</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>配置</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>产品</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>配置状态</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>数据状态</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>配置得分</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>贡献分</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>计分规则</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>对工况影响</t>
         </is>
@@ -35298,14 +35422,17 @@
           <t>三一 SY35U</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>未披露</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
         <v>0.08</v>
       </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
@@ -35644,14 +35771,17 @@
           <t>沃尔沃 EC37</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>未披露</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
         <v>0.06</v>
       </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
@@ -35684,14 +35814,17 @@
           <t>现代 HX35AZ</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>未披露</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
         <v>0.06</v>
       </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
@@ -35724,14 +35857,17 @@
           <t>斗山 DX35Z-7</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>未披露</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
         <v>0.06</v>
       </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
@@ -35764,14 +35900,17 @@
           <t>三一 SY35U</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>未披露</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
         <v>0.06</v>
       </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>标配=100，选配=60，无配置=0，未披露不参与评分</t>
@@ -41412,36 +41551,29 @@
   </sheetPr>
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>工况</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>配置贡献第一</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>第一配置贡献分</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>XCMG配置贡献分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>XCMG配置排名</t>
         </is>
@@ -41586,36 +41718,29 @@
   </sheetPr>
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>工况</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>强相关指标</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>指标权重合计</t>
         </is>
@@ -41772,18 +41897,14 @@
   </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
